--- a/Project 1 Omnichannel Retail Sales/Week 1/RFM_Analysis.xlsx
+++ b/Project 1 Omnichannel Retail Sales/Week 1/RFM_Analysis.xlsx
@@ -5493,7 +5493,7 @@
         <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>886.8200000000001</v>
+        <v>1116.674788381867</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
